--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,6 +3015,130 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 Blade Changes, 1 Screen Change</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,130 +3015,6 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2 Blade Changes, 1 Screen Change</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hdpe</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,6 +3015,340 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 Blade Changes, 1 Screen Change</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>down 60 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Machine running, Hot · down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Steven . A  Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3277,7 +3277,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3285,24 +3285,36 @@
           <t>1st</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>down 60 min (Waiting on material)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3310,29 +3322,41 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>No material  so shut down</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -3340,10 +3364,60 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3351,7 +3351,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3359,12 +3359,24 @@
           <t>1st</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Late start had to wait for material</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3381,7 +3393,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -3389,7 +3401,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3401,7 +3413,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3414,10 +3426,60 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3388,62 +3388,86 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Convey stoped working · down 120 min (Breakdown)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -3451,7 +3475,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3463,7 +3487,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3476,10 +3500,85 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Steven . A  Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3462,95 +3462,143 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Green grass</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Belts broke on grinder had to shut down</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Shut down belts on conveyor motor snapped</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>2 screens changes 2 blade changes · down 120 min</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Steven, Daniel, Jay</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Had one wrap up</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3562,7 +3610,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3575,10 +3623,135 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Steven . A  Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Kemonica was cleaning</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Steven a. Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3610,45 +3610,69 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Kevin, Brandon</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Wrap up 4 times · down 60 min (Other)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>One blade and one screen at starts of shift</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3660,12 +3684,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -3673,7 +3697,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3685,7 +3709,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3698,7 +3722,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3710,12 +3734,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3723,7 +3747,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3735,7 +3759,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3748,10 +3772,85 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
+          <t>Steven . A was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Steven A unloading a truck/cleaning up</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3684,25 +3684,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Machine kept running hot and smoking · down 60 min</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3726,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -3722,7 +3734,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3734,7 +3746,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3747,7 +3759,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3759,7 +3771,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3772,7 +3784,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3784,12 +3796,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -3797,7 +3809,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3814,7 +3826,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -3822,7 +3834,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3834,7 +3846,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3847,10 +3859,85 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
+          <t>Steven a. Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3721,25 +3721,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>material</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3763,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3759,7 +3771,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3771,7 +3783,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3784,7 +3796,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3796,7 +3808,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3809,7 +3821,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3821,12 +3833,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -3834,7 +3846,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3851,7 +3863,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -3859,7 +3871,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3871,7 +3883,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3884,7 +3896,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3896,12 +3908,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3909,7 +3921,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3926,7 +3938,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3934,10 +3946,35 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3758,25 +3758,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3800,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -3796,7 +3808,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3808,7 +3820,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3821,7 +3833,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3833,7 +3845,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3846,7 +3858,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3858,12 +3870,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -3871,7 +3883,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3888,7 +3900,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -3896,7 +3908,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3908,7 +3920,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3921,7 +3933,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3933,12 +3945,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3946,7 +3958,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3963,7 +3975,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -3971,10 +3983,60 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/ cleaning</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3795,20 +3795,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GUILLOTINE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Silicon</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>James, Daniel</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>James helped for 2 hours had a pallet break had to clean up</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3825,7 +3837,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -3833,7 +3845,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3845,7 +3857,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3858,7 +3870,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3870,7 +3882,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3883,7 +3895,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3895,12 +3907,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -3908,7 +3920,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3933,7 +3945,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3945,7 +3957,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3958,7 +3970,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3970,12 +3982,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -3983,7 +3995,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4000,7 +4012,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4008,7 +4020,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4020,7 +4032,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4033,10 +4045,61 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3800,52 +3800,64 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GUILLOTINE</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Silicon</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>James, Daniel</t>
+          <t>Brandon, Montez</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>James helped for 2 hours had a pallet break had to clean up</t>
+          <t>Ran out of material</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>material</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GUILLOTINE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Silicon</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>James, Daniel</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>James helped for 2 hours had a pallet break had to clean up</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3857,32 +3869,44 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3890,29 +3914,41 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>We had it on the belt we had to purge it · down 30 min</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -3920,7 +3956,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3932,12 +3968,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3945,7 +3981,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3957,7 +3993,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3970,7 +4006,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3982,7 +4018,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3995,7 +4031,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4007,7 +4043,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4020,7 +4056,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4032,7 +4068,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4045,7 +4081,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4057,7 +4093,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4070,7 +4106,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4082,12 +4118,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4095,11 +4131,161 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/ cleaning</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>James prepared 27 boxes for shipping 
 And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Clarence was cleaning and bring material</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3943,32 +3943,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Steven B</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>down 60 min</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3976,29 +3988,41 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>We had PT on the belt we had to purge it · down 60 min</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -4006,7 +4030,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4018,7 +4042,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4031,7 +4055,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4043,12 +4067,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4056,7 +4080,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4068,7 +4092,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4081,7 +4105,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4093,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -4106,7 +4130,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4118,12 +4142,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4131,7 +4155,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4143,7 +4167,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4156,7 +4180,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4168,12 +4192,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -4181,7 +4205,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4193,12 +4217,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4206,8 +4230,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4219,12 +4242,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4232,7 +4255,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4249,7 +4272,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -4257,7 +4280,8 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4274,7 +4298,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -4282,10 +4306,110 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
+          <t>Clarence was cleaning and bring material</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>Steven a cleaning</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Had to share tilt lift</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,1406 +3015,6 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2 Blade Changes, 1 Screen Change</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hdpe</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>down 60 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>HDPE</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Machine running, Hot · down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Jay, Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>down 60 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>No material  so shut down</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Late start had to wait for material</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Convey stoped working · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Green grass</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Belts broke on grinder had to shut down</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Shut down belts on conveyor motor snapped</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2 screens changes 2 blade changes · down 120 min</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Steven, Daniel, Jay</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Had one wrap up</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Kevin, Brandon</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Wrap up 4 times · down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>One blade and one screen at starts of shift</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>HDPE</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Machine kept running hot and smoking · down 60 min</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Ran out of material</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>GUILLOTINE</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Silicon</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>James, Daniel</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>James helped for 2 hours had a pallet break had to clean up</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Jay, Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>We had it on the belt we had to purge it · down 30 min</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Steven B</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>down 60 min</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>We had PT on the belt we had to purge it · down 60 min</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Steven . A  Was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Kemonica was cleaning</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Steven a. Was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Steven A unloading a truck/cleaning up</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Kemonica was helping ship/rec</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading/ cleaning</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Clarence was cleaning and bring material</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Had to share tilt lift</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading / cleaning</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,6 +3015,1468 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 Blade Changes, 1 Screen Change</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>down 60 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Machine running, Hot · down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>down 60 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>No material  so shut down</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Late start had to wait for material</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Convey stoped working · down 120 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Green grass</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Belts broke on grinder had to shut down</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Shut down belts on conveyor motor snapped</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2 screens changes 2 blade changes · down 120 min</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Steven, Daniel, Jay</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Had one wrap up</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Kevin, Brandon</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Wrap up 4 times · down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>One blade and one screen at starts of shift</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Machine kept running hot and smoking · down 60 min</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ran out of material</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GUILLOTINE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Silicon</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>James, Daniel</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>James helped for 2 hours had a pallet break had to clean up</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>We had it on the belt we had to purge it · down 30 min</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Steven B</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>down 60 min</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>We had PT on the belt we had to purge it · down 60 min</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Chiller went down</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Steven . A  Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Steven a. Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Steven A unloading a truck/cleaning up</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/ cleaning</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Clarence was cleaning and bring material</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Had to share tilt lift</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Steven A. was unloading</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4054,20 +4054,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Multiple blade change</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4084,7 +4096,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4092,7 +4104,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4104,7 +4116,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4117,7 +4129,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4129,7 +4141,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4142,7 +4154,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4154,12 +4166,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4167,7 +4179,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4184,7 +4196,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4192,7 +4204,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4204,7 +4216,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4217,7 +4229,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4229,12 +4241,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4242,7 +4254,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4259,7 +4271,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4267,7 +4279,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4279,7 +4291,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4292,7 +4304,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4304,12 +4316,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -4317,8 +4329,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4330,12 +4341,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4343,7 +4354,8 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4355,12 +4367,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4368,7 +4380,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4380,7 +4392,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4405,12 +4417,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4418,7 +4430,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4435,7 +4447,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -4443,7 +4455,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4455,7 +4467,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,10 +4480,35 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>Steven A. was unloading</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4091,57 +4091,81 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Came in both belts empty had to do blade and screen change at the start and load both belts than had another blade and screen change total of 2 blades 3 screens · down 125 min (Other)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Guillotine could not keep up had to shut down several times to wait for material · down 120 min (Waiting on material)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4149,29 +4173,41 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Blades broke 3 times had a late start waiting on Montez to get there · down 30 min (Blades)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4179,7 +4215,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4191,12 +4227,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4204,7 +4240,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4216,7 +4252,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4229,7 +4265,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4241,7 +4277,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4254,7 +4290,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4266,7 +4302,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4279,7 +4315,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4291,7 +4327,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4304,7 +4340,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4316,7 +4352,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4329,7 +4365,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4341,12 +4377,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4354,8 +4390,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4367,12 +4402,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4380,7 +4415,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4392,7 +4427,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4405,7 +4440,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4417,12 +4452,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4430,7 +4465,8 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4442,7 +4478,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4455,7 +4491,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4467,7 +4503,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4480,7 +4516,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4492,7 +4528,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4505,10 +4541,135 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Had to share tilt lift</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>Steven A. was unloading</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4202,25 +4202,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>2 blades and 2 screen changes had to find boxes came into no box on the scale · down 120 min (Other)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4244,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4240,7 +4252,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4252,7 +4264,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4265,7 +4277,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4277,7 +4289,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4290,7 +4302,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4302,12 +4314,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4315,7 +4327,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4332,7 +4344,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -4340,7 +4352,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4352,7 +4364,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4365,7 +4377,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4377,12 +4389,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4390,7 +4402,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4407,7 +4419,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4415,7 +4427,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4427,7 +4439,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4440,7 +4452,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4452,12 +4464,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4465,8 +4477,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4478,12 +4489,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -4491,7 +4502,8 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4503,12 +4515,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -4516,7 +4528,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4528,7 +4540,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4553,12 +4565,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4566,7 +4578,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4583,7 +4595,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4591,7 +4603,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4603,7 +4615,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4616,7 +4628,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4628,12 +4640,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4641,24 +4653,24 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -4666,10 +4678,35 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,62 +4239,86 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>And I did a screen change · down 30 min (Blades)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Blade and screen change x2 · down 60 min</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4302,7 +4326,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4314,7 +4338,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4327,7 +4351,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4339,12 +4363,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -4352,7 +4376,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4364,7 +4388,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4377,7 +4401,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4389,12 +4413,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4402,7 +4426,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4414,12 +4438,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4427,7 +4451,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4439,7 +4463,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4452,7 +4476,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4464,12 +4488,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4477,7 +4501,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4489,12 +4513,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -4502,8 +4526,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4515,12 +4538,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -4528,7 +4551,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4545,7 +4568,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4553,7 +4576,8 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4570,7 +4594,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4578,7 +4602,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4590,12 +4614,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4603,7 +4627,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4615,7 +4639,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4628,7 +4652,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4640,12 +4664,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4653,7 +4677,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4665,12 +4689,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -4678,19 +4702,19 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4703,10 +4727,85 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
+          <t>Steven A. was unloading</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4313,20 +4313,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Did 3 blade changes and a screen change</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4338,20 +4350,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>1 screen and 1 blade change</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4363,12 +4387,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -4376,7 +4400,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4388,7 +4412,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4401,7 +4425,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4413,12 +4437,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4426,7 +4450,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4438,7 +4462,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4451,7 +4475,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4463,12 +4487,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -4476,7 +4500,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4488,12 +4512,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4501,7 +4525,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4513,7 +4537,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4526,7 +4550,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4538,12 +4562,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -4551,7 +4575,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4563,12 +4587,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4576,8 +4600,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4589,12 +4612,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4602,7 +4625,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4619,7 +4642,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4627,7 +4650,8 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4644,7 +4668,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4652,7 +4676,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4664,12 +4688,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4677,7 +4701,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4689,7 +4713,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4702,7 +4726,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4714,12 +4738,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4727,7 +4751,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4739,12 +4763,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4752,19 +4776,19 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4777,7 +4801,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4789,12 +4813,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4802,10 +4826,60 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4387,7 +4387,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4395,37 +4395,61 @@
           <t>1st</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Jay, Daniel</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Shredder went down waiting on parts to come in</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4437,7 +4461,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4445,24 +4469,36 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Steven B</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Maintenance · down 240 min (Other)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4470,24 +4506,36 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Maintenance · down 120 min (Other)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4500,7 +4548,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4512,7 +4560,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4525,7 +4573,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4537,7 +4585,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4550,7 +4598,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4562,12 +4610,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -4575,7 +4623,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4587,12 +4635,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4600,7 +4648,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4612,7 +4660,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4625,7 +4673,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4637,12 +4685,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4650,8 +4698,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4663,7 +4710,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4676,7 +4723,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4688,7 +4735,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4701,7 +4748,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4713,7 +4760,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4726,7 +4773,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4738,12 +4785,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4751,7 +4798,8 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4763,12 +4811,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4776,7 +4824,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4788,7 +4836,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4801,7 +4849,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4813,12 +4861,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4826,24 +4874,24 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4851,7 +4899,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4863,7 +4911,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4876,10 +4924,135 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Steven A. was unloading</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5058,31 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,25 +4535,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Bridgestone and cardboard</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Strap stoped working or lost power so shut down</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4577,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4573,7 +4585,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4585,7 +4597,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4598,7 +4610,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4610,7 +4622,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4623,7 +4635,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4635,12 +4647,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4648,7 +4660,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4665,7 +4677,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4673,7 +4685,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4685,7 +4697,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4698,7 +4710,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4710,12 +4722,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4723,7 +4735,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4740,7 +4752,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4748,7 +4760,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4760,7 +4772,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4773,7 +4785,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4785,12 +4797,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4798,8 +4810,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4811,12 +4822,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4824,7 +4835,8 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4836,12 +4848,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -4849,7 +4861,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4861,7 +4873,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4886,12 +4898,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4899,7 +4911,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4916,7 +4928,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -4924,7 +4936,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4936,7 +4948,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4949,7 +4961,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4961,12 +4973,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -4974,24 +4986,24 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -4999,19 +5011,19 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5024,7 +5036,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5036,7 +5048,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5049,7 +5061,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5061,7 +5073,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5074,10 +5086,60 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Steven a and Brandon was cleaning</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4572,45 +4572,69 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Had 3 wrap ups and change the blades 3 times · down 120 min (Breakdown)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>1 blade 1 screen change at start of shift</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4622,12 +4646,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -4635,7 +4659,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4647,7 +4671,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4660,7 +4684,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4672,12 +4696,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4685,7 +4709,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4697,7 +4721,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4710,7 +4734,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4722,12 +4746,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4735,7 +4759,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4747,12 +4771,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4760,7 +4784,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4772,7 +4796,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4785,7 +4809,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4797,12 +4821,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4810,7 +4834,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4822,12 +4846,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4835,8 +4859,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4848,12 +4871,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -4861,7 +4884,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4878,7 +4901,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4886,7 +4909,8 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4903,7 +4927,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4911,7 +4935,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4923,12 +4947,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -4936,7 +4960,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4948,7 +4972,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4961,7 +4985,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4973,12 +4997,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -4986,7 +5010,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4998,12 +5022,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -5011,19 +5035,19 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5036,7 +5060,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5048,12 +5072,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5061,19 +5085,19 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5086,7 +5110,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5098,7 +5122,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5111,7 +5135,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5123,7 +5147,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5136,10 +5160,110 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
           <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning and moving material</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>The new guy was on the extruder too</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4646,7 +4646,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4654,12 +4654,24 @@
           <t>1st</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GPPS/HIPS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4671,7 +4683,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4679,29 +4691,41 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Maintenance did screen change and had to change the blades 3 times · down 60 min</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4709,7 +4733,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4721,7 +4745,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4734,7 +4758,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4746,12 +4770,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4759,7 +4783,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4771,7 +4795,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4784,7 +4808,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4796,12 +4820,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -4809,7 +4833,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4821,12 +4845,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4834,7 +4858,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4846,7 +4870,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4859,7 +4883,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4871,12 +4895,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -4884,7 +4908,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4896,12 +4920,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4909,8 +4933,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4922,12 +4945,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4935,7 +4958,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4952,7 +4975,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -4960,7 +4983,8 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4977,7 +5001,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4985,7 +5009,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4997,12 +5021,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5010,7 +5034,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5022,7 +5046,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5035,7 +5059,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5047,12 +5071,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5060,7 +5084,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5072,12 +5096,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5085,19 +5109,19 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5110,7 +5134,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5122,12 +5146,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5135,19 +5159,19 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5160,7 +5184,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5172,7 +5196,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5185,7 +5209,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5197,7 +5221,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5210,7 +5234,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5222,12 +5246,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5235,7 +5259,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5247,7 +5271,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5260,10 +5284,85 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
+          <t>Steven a and Brandon was cleaning</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning and moving material</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>The new guy was on the extruder too</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4720,25 +4720,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>3 blade changes and 1 screen change · down 60 min</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4762,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4758,7 +4770,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4770,7 +4782,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4783,7 +4795,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4795,7 +4807,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4808,7 +4820,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4820,12 +4832,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -4833,7 +4845,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4850,7 +4862,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4858,7 +4870,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4870,7 +4882,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4883,7 +4895,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4895,12 +4907,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -4908,7 +4920,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4925,7 +4937,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4933,7 +4945,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4945,7 +4957,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4958,7 +4970,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4970,12 +4982,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -4983,8 +4995,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4996,12 +5007,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5009,7 +5020,8 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5021,12 +5033,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5034,7 +5046,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5046,7 +5058,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5071,12 +5083,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5084,7 +5096,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5101,7 +5113,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5109,7 +5121,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5121,7 +5133,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5134,7 +5146,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5146,12 +5158,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5159,24 +5171,24 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5184,19 +5196,19 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5209,7 +5221,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5221,7 +5233,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5234,7 +5246,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5246,7 +5258,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5259,7 +5271,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5271,7 +5283,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5284,7 +5296,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5296,12 +5308,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5309,7 +5321,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5326,7 +5338,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5334,7 +5346,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5346,7 +5358,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5359,10 +5371,35 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
+          <t>The new guy was on the extruder too</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>Steven a was cleaning</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,2396 +3015,6 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2 Blade Changes, 1 Screen Change</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hdpe</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>down 60 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>HDPE</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Machine running, Hot · down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Jay, Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>down 60 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>No material  so shut down</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Late start had to wait for material</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Convey stoped working · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Green grass</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Belts broke on grinder had to shut down</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Shut down belts on conveyor motor snapped</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2 screens changes 2 blade changes · down 120 min</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Steven, Daniel, Jay</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Had one wrap up</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Kevin, Brandon</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Wrap up 4 times · down 60 min (Other)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>One blade and one screen at starts of shift</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SHREDDER</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>HDPE</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Machine kept running hot and smoking · down 60 min</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Ran out of material</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>GUILLOTINE</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Silicon</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>James, Daniel</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>James helped for 2 hours had a pallet break had to clean up</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Jay, Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Brandon, Montez</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>We had it on the belt we had to purge it · down 30 min</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Mixed Plastic</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Steven B</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>down 60 min</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>We had PT on the belt we had to purge it · down 60 min</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Steven, Daniel</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Chiller went down</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Multiple blade change</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Came in both belts empty had to do blade and screen change at the start and load both belts than had another blade and screen change total of 2 blades 3 screens · down 125 min (Other)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Guillotine could not keep up had to shut down several times to wait for material · down 120 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Blades broke 3 times had a late start waiting on Montez to get there · down 30 min (Blades)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2 blades and 2 screen changes had to find boxes came into no box on the scale · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>And I did a screen change · down 30 min (Blades)</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Blade and screen change x2 · down 60 min</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Did 3 blade changes and a screen change</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1 screen and 1 blade change</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Jay, Daniel</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Shredder went down waiting on parts to come in</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Hdpe</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Steven B</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Maintenance · down 240 min (Other)</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Maintenance · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Bridgestone and cardboard</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Strap stoped working or lost power so shut down</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Had 3 wrap ups and change the blades 3 times · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>1 blade 1 screen change at start of shift</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>GPPS/HIPS</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Brandon Marcus</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Maintenance did screen change and had to change the blades 3 times · down 60 min</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>3 blade changes and 1 screen change · down 60 min</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Steven . A  Was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Kemonica was cleaning</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Steven a. Was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Steven A unloading a truck/cleaning up</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Kemonica was helping ship/rec</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading/ cleaning</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Clarence was cleaning and bring material</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Had to share tilt lift</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading / cleaning</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Steven A. was unloading</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Steven a and Brandon was cleaning</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Kemonica was cleaning and moving material</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>The new guy was on the extruder too</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Steven a was cleaning</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3015,6 +3015,2534 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 Blade Changes, 1 Screen Change</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>down 60 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Machine running, Hot · down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>down 60 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>No material  so shut down</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LDPE green grass regrind</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Had to replace fuse 1,2,and 3 than blower got clogged there was also no converting page for 3rd shift weight is put on 2nd shift · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Late start had to wait for material</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Convey stoped working · down 120 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Green grass</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Belts broke on grinder had to shut down</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Shut down belts on conveyor motor snapped</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2 screens changes 2 blade changes · down 120 min</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Steven, Daniel, Jay</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Had one wrap up</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kevin, Brandon</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Wrap up 4 times · down 60 min (Other)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>One blade and one screen at starts of shift</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SHREDDER</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Machine kept running hot and smoking · down 60 min</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ran out of material</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GUILLOTINE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Silicon</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>James, Daniel</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>James helped for 2 hours had a pallet break had to clean up</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Jay, Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Brandon, Montez</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>We had it on the belt we had to purge it · down 30 min</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mixed Plastic</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Steven B</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>down 60 min</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>We had PT on the belt we had to purge it · down 60 min</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Chiller went down</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Moved James over after issues with densifier</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Montez, Brandon</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Multiple blade change</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Came in both belts empty had to do blade and screen change at the start and load both belts than had another blade and screen change total of 2 blades 3 screens · down 125 min (Other)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Guillotine could not keep up had to shut down several times to wait for material · down 120 min (Waiting on material)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blades broke 3 times had a late start waiting on Montez to get there · down 30 min (Blades)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2 blades and 2 screen changes had to find boxes came into no box on the scale · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>And I did a screen change · down 30 min (Blades)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Blade and screen change x2 · down 60 min</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Did 3 blade changes and a screen change</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 screen and 1 blade change</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Jay, Daniel</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Shredder went down waiting on parts to come in</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Hdpe</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Steven B</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Maintenance · down 240 min (Other)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Maintenance · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Bridgestone and cardboard</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Strap stoped working or lost power so shut down</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Brandon, Steven A</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Had 3 wrap ups and change the blades 3 times · down 120 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1 blade 1 screen change at start of shift</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GPPS/HIPS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Maintenance did screen change and had to change the blades 3 times · down 60 min</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>3 blade changes and 1 screen change · down 60 min</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Blade and screen change at start 
+1 blade broke
+Had to clean and get organized before start · down 120 min (Other)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Steven . A  Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Steven a. Was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Steven A unloading a truck/cleaning up</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kemonica was helping ship/rec</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Steven . A  was unloading/cleaning</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/ cleaning</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Clarence was cleaning and bring material</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Had to share tilt lift</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Steven A. was unloading</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Steven a and Brandon was cleaning</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning and moving material</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>The new guy was on the extruder too</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4870,20 +4870,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Did 3 blade changes and a screen change</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4900,7 +4912,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4908,7 +4920,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4920,7 +4932,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4933,7 +4945,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4945,7 +4957,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4958,7 +4970,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4970,12 +4982,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4983,7 +4995,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5000,7 +5012,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -5008,7 +5020,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5020,7 +5032,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5033,7 +5045,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5045,12 +5057,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5058,7 +5070,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5075,7 +5087,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5083,7 +5095,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5095,7 +5107,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5108,7 +5120,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5120,12 +5132,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5133,8 +5145,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5146,12 +5157,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5159,7 +5170,8 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5171,12 +5183,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -5184,7 +5196,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5196,7 +5208,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5221,12 +5233,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5234,7 +5246,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5251,7 +5263,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5259,7 +5271,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5271,7 +5283,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5284,7 +5296,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5296,12 +5308,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5309,24 +5321,24 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5334,19 +5346,19 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5359,7 +5371,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5371,7 +5383,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5384,7 +5396,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5396,7 +5408,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5409,7 +5421,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5421,7 +5433,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5434,7 +5446,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5446,12 +5458,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5459,7 +5471,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5476,7 +5488,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5484,7 +5496,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5496,7 +5508,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5509,7 +5521,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5521,12 +5533,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -5534,10 +5546,60 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
           <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4907,20 +4907,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>1 screen change one blade change at start of shift</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4932,45 +4944,69 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Cores</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Belt was cut up had to wait for maintenance</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Steven, Daniel</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>3 blade changes</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4982,20 +5018,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Grinder had a melt up had to open and clean/burn material out of screen</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5007,20 +5055,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Brandon, Kevin Marcus</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Did 2 blade changes</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5032,12 +5092,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -5045,7 +5105,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5057,7 +5117,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5070,7 +5130,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5082,12 +5142,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5095,7 +5155,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5107,7 +5167,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5120,7 +5180,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5132,12 +5192,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5145,7 +5205,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5157,12 +5217,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5170,8 +5230,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5183,12 +5242,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -5196,7 +5255,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5208,12 +5267,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5221,7 +5280,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5233,7 +5292,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5246,7 +5305,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5258,12 +5317,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5271,7 +5330,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5283,12 +5342,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5296,7 +5355,8 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5308,12 +5368,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5321,7 +5381,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5333,12 +5393,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5346,19 +5406,19 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5371,7 +5431,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5383,12 +5443,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5396,7 +5456,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5408,7 +5468,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5421,7 +5481,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5433,7 +5493,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5446,7 +5506,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5458,12 +5518,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5471,24 +5531,24 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5496,7 +5556,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5508,7 +5568,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5521,7 +5581,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5533,7 +5593,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5546,7 +5606,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5558,12 +5618,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -5571,7 +5631,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5583,7 +5643,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5596,10 +5656,160 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
+          <t>Steven a and Brandon was cleaning</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning and moving material</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>The new guy was on the extruder too</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
           <t>Steven a was cleaning</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5092,25 +5092,39 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Connor, Daniel</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Screen change and blades at start of shift 
+Cutter backup at 2:30 had to clean cutter out
+Than do another screen and blade change · down 90 min</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5136,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5130,7 +5144,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5142,7 +5156,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5155,7 +5169,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5167,7 +5181,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5180,7 +5194,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5192,12 +5206,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5205,7 +5219,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5222,7 +5236,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5230,7 +5244,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5242,7 +5256,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5255,7 +5269,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5267,12 +5281,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5280,7 +5294,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5297,7 +5311,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5305,7 +5319,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5317,7 +5331,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5330,7 +5344,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5342,12 +5356,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5355,8 +5369,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5368,12 +5381,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5381,7 +5394,8 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5393,12 +5407,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5406,7 +5420,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5418,7 +5432,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5443,12 +5457,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5456,7 +5470,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5473,7 +5487,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -5481,7 +5495,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5493,7 +5507,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5506,7 +5520,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5518,12 +5532,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5531,24 +5545,24 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5556,19 +5570,19 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5581,7 +5595,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5593,7 +5607,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5606,7 +5620,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5618,7 +5632,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5631,7 +5645,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5643,7 +5657,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5656,7 +5670,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5668,12 +5682,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -5681,7 +5695,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5698,7 +5712,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -5706,7 +5720,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5718,7 +5732,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5731,7 +5745,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5743,12 +5757,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -5756,7 +5770,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5768,12 +5782,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -5781,7 +5795,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5793,7 +5807,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5806,10 +5820,85 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
           <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5131,25 +5131,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Brandon, Marcus</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Change the blades 3 times and had 2 wrap up’s and had to purge the machine out did two screen changes · down 160 min (Breakdown)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5173,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5169,7 +5181,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5181,7 +5193,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5194,7 +5206,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5206,7 +5218,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5219,7 +5231,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven . A  Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5231,12 +5243,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5244,7 +5256,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Steven . A was unloading/cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5261,7 +5273,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -5269,7 +5281,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Kemonica was cleaning</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5281,7 +5293,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5294,7 +5306,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven A unloading a truck/cleaning up</t>
+          <t>Steven a. Was unloading/cleaning</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5306,12 +5318,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5319,7 +5331,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kemonica was helping ship/rec</t>
+          <t>Steven A unloading a truck/cleaning up</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5336,7 +5348,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5344,7 +5356,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Kemonica was helping ship/rec</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5356,7 +5368,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5369,7 +5381,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Steven . A  was unloading/cleaning</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5381,12 +5393,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5394,8 +5406,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5407,12 +5418,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5420,7 +5431,8 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5432,12 +5444,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5445,7 +5457,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5457,7 +5469,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5482,12 +5494,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -5495,7 +5507,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5512,7 +5524,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -5520,7 +5532,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5532,7 +5544,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5545,7 +5557,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5557,12 +5569,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5570,24 +5582,24 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -5595,19 +5607,19 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5620,7 +5632,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5632,7 +5644,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5645,7 +5657,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5657,7 +5669,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5670,7 +5682,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5682,7 +5694,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5695,7 +5707,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5707,12 +5719,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -5720,7 +5732,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5737,7 +5749,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -5745,7 +5757,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5757,7 +5769,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5770,7 +5782,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5782,12 +5794,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -5795,7 +5807,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5807,12 +5819,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -5820,7 +5832,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5832,7 +5844,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5845,7 +5857,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5862,7 +5874,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -5870,7 +5882,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5882,12 +5894,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -5895,10 +5907,85 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
           <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Anthony was cleaning outside</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3018,7 +3018,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3038,24 +3038,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Connor, James</t>
+          <t>James, Connor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2 Blade Changes, 1 Screen Change</t>
+          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3065,71 +3065,71 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SHREDDER</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Hdpe</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Brandon, Montez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>down 60 min (Other)</t>
+          <t>Ran out of material</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>material</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AUTO TIE BALER</t>
+          <t>GUILLOTINE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mixed Plastic</t>
+          <t>Silicon</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>James, Daniel</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Had to full with oil then maintenance had to fix the track from catching · down 120 min (Other)</t>
+          <t>James helped for 2 hours had a pallet break had to clean up</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Steven, Daniel</t>
+          <t>Jay, Steven, Daniel</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>down 60 min (Waiting on material)</t>
+          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montez, Brandon</t>
+          <t>Brandon, Montez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>We had PT on the belt and we had to purge it · down 120 min (Waiting on material)</t>
+          <t>We had it on the belt we had to purge it · down 30 min</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SHREDDER</t>
+          <t>AUTO TIE BALER</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HDPE</t>
+          <t>Mixed Plastic</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Steven B</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Machine running, Hot · down 60 min (Other)</t>
+          <t>down 60 min</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3240,12 +3240,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>James, Connor</t>
+          <t>Montez, Brandon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4 screens 3 blade changes had to clean line and purge system one of the conveyor belts went down · down 180 min (Other)</t>
+          <t>We had PT on the belt we had to purge it · down 60 min</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jay, Steven, Daniel</t>
+          <t>Steven, Daniel</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>down 60 min (Waiting on material)</t>
+          <t>Chiller went down</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3314,86 +3314,86 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EXTRUDER</t>
+          <t>GRINDER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BOPP resin</t>
+          <t>LDPE</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Brandon, Montez</t>
+          <t>Connor, James</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>No material  so shut down</t>
+          <t>Moved James over after issues with densifier</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GRINDER</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LDPE green grass regrind</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Montez, Brandon</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Had to replace fuse 1,2,and 3 than blower got clogged there was also no converting page for 3rd shift weight is put on 2nd shift · down 180 min (Other)</t>
+          <t>Multiple blade change</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3408,49 +3408,49 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Steven, Daniel</t>
+          <t>James, Connor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Late start had to wait for material</t>
+          <t>Came in both belts empty had to do blade and screen change at the start and load both belts than had another blade and screen change total of 2 blades 3 screens · down 125 min (Other)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AUTO TIE BALER</t>
+          <t>GRINDER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mixed Plastic</t>
+          <t>LDPE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Convey stoped working · down 120 min (Breakdown)</t>
+          <t>Guillotine could not keep up had to shut down several times to wait for material · down 120 min (Waiting on material)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Connor, James</t>
+          <t>Brandon, Steven A</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7 screen changes 2 blade changes had to cut material had trash on line and in system had to clean and purge system · down 300 min (Other)</t>
+          <t>Blades broke 3 times had a late start waiting on Montez to get there · down 30 min (Blades)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3499,32 +3499,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GRINDER</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Green grass</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>James, Connor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Belts broke on grinder had to shut down</t>
+          <t>2 blades and 2 screen changes had to find boxes came into no box on the scale · down 120 min (Other)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3536,32 +3536,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AUTO TIE BALER</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mixed Plastic</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Brandon, Steven A</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shut down belts on conveyor motor snapped</t>
+          <t>And I did a screen change · down 30 min (Blades)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2 screens changes 2 blade changes · down 120 min</t>
+          <t>Blade and screen change x2 · down 60 min</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3610,12 +3610,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Steven, Daniel, Jay</t>
+          <t>Brandon, Steven A</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Had one wrap up</t>
+          <t>Did 3 blade changes and a screen change</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3667,29 +3667,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kevin, Brandon</t>
+          <t>Connor, James</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wrap up 4 times · down 60 min (Other)</t>
+          <t>1 screen and 1 blade change</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3704,123 +3704,123 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Connor, James</t>
+          <t>Jay, Daniel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>One blade and one screen at starts of shift</t>
+          <t>Shredder went down waiting on parts to come in</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SHREDDER</t>
+          <t>GRINDER</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>HDPE</t>
+          <t>LDPE</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Machine kept running hot and smoking · down 60 min</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EXTRUDER</t>
+          <t>AUTO TIE BALER</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BOPP resin</t>
+          <t>Hdpe</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>James, Connor</t>
+          <t>Steven B</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blade and screen change at start of shift also ran out of material before end of shift made lil over 6500 pounds</t>
+          <t>Maintenance · down 240 min (Other)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EXTRUDER</t>
+          <t>GRINDER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BOPP resin</t>
+          <t>LDPE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>James, Connor</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2 screen change had to find material 2 blade change · down 180 min (Other)</t>
+          <t>Maintenance · down 120 min (Other)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3832,86 +3832,86 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EXTRUDER</t>
+          <t>AUTO TIE BALER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BOPP resin</t>
+          <t>Bridgestone and cardboard</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brandon, Montez</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ran out of material</t>
+          <t>Strap stoped working or lost power so shut down</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GUILLOTINE</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Silicon</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>James, Daniel</t>
+          <t>Brandon, Steven A</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>James helped for 2 hours had a pallet break had to clean up</t>
+          <t>Had 3 wrap ups and change the blades 3 times · down 120 min (Breakdown)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3926,61 +3926,61 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jay, Steven, Daniel</t>
+          <t>Connor, James</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Started late then had to have maintenance fix the power switch for the belt · down 120 min (Breakdown)</t>
+          <t>1 blade 1 screen change at start of shift</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EXTRUDER</t>
+          <t>GRINDER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>BOPP resin</t>
+          <t>GPPS/HIPS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brandon, Montez</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>We had it on the belt we had to purge it · down 30 min</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3990,22 +3990,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AUTO TIE BALER</t>
+          <t>EXTRUDER</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mixed Plastic</t>
+          <t>BOPP resin</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Steven B</t>
+          <t>Brandon Marcus</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>down 60 min</t>
+          <t>Maintenance did screen change and had to change the blades 3 times · down 60 min</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4017,12 +4017,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Montez, Brandon</t>
+          <t>James, Connor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>We had PT on the belt we had to purge it · down 60 min</t>
+          <t>3 blade changes and 1 screen change · down 60 min</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4054,12 +4054,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4074,1064 +4074,837 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Steven, Daniel</t>
+          <t>James, Connor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
-        <is>
-          <t>Chiller went down</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Moved James over after issues with densifier</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Montez, Brandon</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Multiple blade change</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Came in both belts empty had to do blade and screen change at the start and load both belts than had another blade and screen change total of 2 blades 3 screens · down 125 min (Other)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Tim</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Guillotine could not keep up had to shut down several times to wait for material · down 120 min (Waiting on material)</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Blades broke 3 times had a late start waiting on Montez to get there · down 30 min (Blades)</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2 blades and 2 screen changes had to find boxes came into no box on the scale · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>And I did a screen change · down 30 min (Blades)</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Blade and screen change x2 · down 60 min</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Did 3 blade changes and a screen change</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1 screen and 1 blade change</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Jay, Daniel</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Shredder went down waiting on parts to come in</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Hdpe</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Steven B</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Maintenance · down 240 min (Other)</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>LDPE</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Maintenance · down 120 min (Other)</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AUTO TIE BALER</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Bridgestone and cardboard</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Darius</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Strap stoped working or lost power so shut down</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Brandon, Steven A</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Had 3 wrap ups and change the blades 3 times · down 120 min (Breakdown)</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Connor, James</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>1 blade 1 screen change at start of shift</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>GPPS/HIPS</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Brandon Marcus</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Maintenance did screen change and had to change the blades 3 times · down 60 min</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>3 blade changes and 1 screen change · down 60 min</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>James, Connor</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>Blade and screen change at start 
 1 blade broke
 Had to clean and get organized before start · down 120 min (Other)</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>downtime</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>EXTRUDER</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>BOPP resin</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Brandon Marcus</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Did 3 blade changes and a screen change</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>EXTRUDER</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>BOPP resin</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>James, Connor</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>1 screen change one blade change at start of shift</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>AUTO TIE BALER</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Cores</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Tony</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Belt was cut up had to wait for maintenance</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>downtime</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>EXTRUDER</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>BOPP resin</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Steven, Daniel</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>3 blade changes</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>GRINDER</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>LDPE</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Anthony</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Grinder had a melt up had to open and clean/burn material out of screen</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
         <is>
           <t>EXTRUDER</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>BOPP resin</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Brandon, Kevin Marcus</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Did 2 blade changes</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>EXTRUDER</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>BOPP resin</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Connor, Daniel</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Screen change and blades at start of shift 
 Cutter backup at 2:30 had to clean cutter out
 Than do another screen and blade change · down 90 min</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Brandon, Marcus</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Change the blades 3 times and had 2 wrap up’s and had to purge the machine out did two screen changes · down 160 min (Breakdown)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Did 2 blade changes and had a small wrap up when I first started</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading/ cleaning</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Clarence was cleaning and bring material</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Steven a cleaning</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Had to share tilt lift</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Steven . A was unloading / cleaning</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Steven A. was unloading</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Steven a and Brandon was cleaning</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Kemonica was cleaning and moving material</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>The new guy was on the extruder too</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5139,41 +4912,29 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>EXTRUDER</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>BOPP resin</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Brandon, Marcus</t>
-        </is>
-      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Change the blades 3 times and had 2 wrap up’s and had to purge the machine out did two screen changes · down 160 min (Breakdown)</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5181,7 +4942,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5193,7 +4954,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5206,7 +4967,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven . A  was unloading/cleaning</t>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5218,12 +4979,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5231,7 +4992,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven . A  Was unloading/cleaning</t>
+          <t>Anthony was cleaning outside</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5243,7 +5004,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5256,7 +5017,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5268,7 +5029,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5281,7 +5042,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5293,7 +5054,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5306,686 +5067,10 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven a. Was unloading/cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Steven A unloading a truck/cleaning up</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Kemonica was helping ship/rec</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Steven . A  was unloading/cleaning</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading/ cleaning</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Clarence was cleaning and bring material</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Steven a cleaning</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Had to share tilt lift</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Steven . A was unloading / cleaning</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Steven A. was unloading</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Steven a and Brandon was cleaning</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Kemonica was cleaning and moving material</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>The new guy was on the extruder too</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Steven a was cleaning</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Steven a was cleaning</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Anthony was cleaning outside</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Steven a was cleaning</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4428,45 +4428,70 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Screen and blade change at beginning 
+Than another blade change in middle of shift · down 30 min (Blades)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Kemonica Anthony</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Anthony turned off the grinder with material inside running had to open and clean out</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4478,12 +4503,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4491,8 +4516,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4504,12 +4528,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -4517,7 +4541,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4529,12 +4553,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -4542,7 +4566,8 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4554,7 +4579,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4567,7 +4592,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4579,7 +4604,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4592,7 +4617,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4604,12 +4629,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4617,7 +4642,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4629,12 +4654,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4642,19 +4667,19 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4667,7 +4692,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4679,12 +4704,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4692,19 +4717,19 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4717,7 +4742,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4729,7 +4754,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4742,7 +4767,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4754,7 +4779,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4767,7 +4792,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4779,12 +4804,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4792,7 +4817,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4804,7 +4829,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4817,7 +4842,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4829,12 +4854,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4842,7 +4867,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4854,12 +4879,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4867,7 +4892,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4879,7 +4904,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4904,12 +4929,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4917,7 +4942,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4929,12 +4954,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -4942,7 +4967,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4954,7 +4979,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4967,7 +4992,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4979,12 +5004,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -4992,7 +5017,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anthony was cleaning outside</t>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5004,7 +5029,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5017,7 +5042,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5029,7 +5054,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5042,7 +5067,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Anthony was cleaning outside</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5054,7 +5079,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5076,6 +5101,81 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tony was cleaning around the auto tie</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4503,7 +4503,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4511,12 +4511,24 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Did 2 blade changes</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4528,46 +4540,70 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Connor, James</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Had to locate and prepare boxes 
+Do screen and blade change before starting · down 60 min (Other)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Had to run machine out so maintenance could weld on the shredder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4579,12 +4615,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -4592,7 +4628,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4604,7 +4640,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4629,12 +4665,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4642,7 +4678,8 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4654,12 +4691,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4667,7 +4704,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4679,7 +4716,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4692,7 +4729,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4704,12 +4741,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4717,19 +4754,19 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4742,7 +4779,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4754,7 +4791,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4767,7 +4804,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4779,12 +4816,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4792,19 +4829,19 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4817,7 +4854,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4829,7 +4866,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4842,7 +4879,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4854,12 +4891,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4867,7 +4904,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4879,7 +4916,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4892,7 +4929,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4904,7 +4941,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4917,7 +4954,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4929,7 +4966,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4942,7 +4979,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4954,7 +4991,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4967,7 +5004,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4979,7 +5016,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4992,7 +5029,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5004,12 +5041,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5017,7 +5054,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5029,7 +5066,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5042,7 +5079,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5054,12 +5091,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -5067,7 +5104,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anthony was cleaning outside</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5079,12 +5116,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5092,7 +5129,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5104,12 +5141,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5117,7 +5154,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5129,12 +5166,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5142,7 +5179,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Anthony was cleaning outside</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5154,12 +5191,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5167,10 +5204,135 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>Tony was cleaning around the auto tie</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Both Steven’s was cleaning and Steven a was also unloading a truck</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Darius clean around autoroute for first 3 hours of shift</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4615,7 +4615,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4623,12 +4623,24 @@
           <t>2nd</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>Did 2 blade changes</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4640,7 +4652,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4653,7 +4665,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4670,7 +4682,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -4678,8 +4690,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4691,12 +4702,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -4704,7 +4715,8 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4721,7 +4733,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4729,7 +4741,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4741,12 +4753,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4754,7 +4766,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4771,7 +4783,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4779,7 +4791,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4791,7 +4803,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4804,7 +4816,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4816,12 +4828,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4829,24 +4841,24 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4854,19 +4866,19 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4879,7 +4891,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4891,7 +4903,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4904,7 +4916,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4916,7 +4928,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4929,7 +4941,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4941,7 +4953,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4954,7 +4966,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4966,12 +4978,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4979,7 +4991,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4996,7 +5008,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5004,7 +5016,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5016,7 +5028,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5029,7 +5041,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5041,12 +5053,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5054,7 +5066,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5066,12 +5078,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5079,7 +5091,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5091,7 +5103,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5104,7 +5116,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5121,7 +5133,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5129,7 +5141,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5141,12 +5153,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5154,7 +5166,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5166,12 +5178,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5179,7 +5191,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Anthony was cleaning outside</t>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5196,7 +5208,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5204,7 +5216,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Anthony was cleaning outside</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5216,12 +5228,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5229,7 +5241,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5246,7 +5258,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5254,7 +5266,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5266,12 +5278,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5279,7 +5291,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tony was cleaning around the auto tie</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5296,7 +5308,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5304,7 +5316,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Both Steven’s was cleaning and Steven a was also unloading a truck</t>
+          <t>Tony was cleaning around the auto tie</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5321,7 +5333,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -5329,10 +5341,60 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
+          <t>Both Steven’s was cleaning and Steven a was also unloading a truck</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>Darius clean around autoroute for first 3 hours of shift</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>operational</t>
         </is>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4652,20 +4652,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>GREEN MAX DENSIFIER (NEW)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kemonica</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Steven . A was unloading/ cleaning</t>
+          <t>E-stop was damaged had to troubleshoot then had to bypass it.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4677,20 +4689,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LDPE</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Blew a fuse twice</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4702,21 +4726,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Brandon Marcus</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>James prepared 27 boxes for shipping 
-And cleaned and got shredder grinder ready to run for 10/1/26</t>
+          <t>Did 2 blade changes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4728,20 +4763,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Green grass</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Tevin</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Clarence was cleaning and bring material</t>
+          <t>Material got mixed up</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4753,37 +4800,51 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EXTRUDER</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BOPP resin</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>James, Connor</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Steven a cleaning</t>
+          <t>Blade change and screen at start of shift 
+Blade change halfway through shift 
+Also had to change water filter and reset chiller and weight for temperature to readjust · down 120 min (Other)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4791,7 +4852,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Had to share tilt lift</t>
+          <t>Steven . A was unloading/ cleaning</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4803,7 +4864,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4816,7 +4877,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Steven . A was unloading / cleaning</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4828,12 +4889,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -4841,7 +4902,8 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Steven A. was unloading</t>
+          <t>James prepared 27 boxes for shipping 
+And cleaned and got shredder grinder ready to run for 10/1/26</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4853,12 +4915,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4866,19 +4928,19 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
+          <t>Clarence was cleaning and bring material</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>downtime</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4891,7 +4953,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
+          <t>Steven a cleaning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4903,12 +4965,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4916,7 +4978,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Had to change the blades 3 to 4 times on the extruder.</t>
+          <t>Had to share tilt lift</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4928,7 +4990,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4941,7 +5003,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Steven A cleaning Brandon cleaning/maintenance</t>
+          <t>Steven . A was unloading / cleaning</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4953,7 +5015,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4966,7 +5028,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
+          <t>Steven A. was unloading</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4978,12 +5040,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4991,24 +5053,24 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Steven a and Brandon was cleaning</t>
+          <t>I have pictures of how the belts where left when we came in please let me know who to send them too</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>downtime</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -5016,7 +5078,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kemonica was cleaning and moving material</t>
+          <t>Steven was unloading a truck but came to the extruder with Brandon because Montez left</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5028,7 +5090,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5041,7 +5103,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>The new guy was on the extruder too</t>
+          <t>Had to change the blades 3 to 4 times on the extruder.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5053,7 +5115,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5066,7 +5128,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Steven A cleaning Brandon cleaning/maintenance</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5078,12 +5140,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5091,7 +5153,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kemonica was grabbing material for various machines and cleaning</t>
+          <t>Steven a unloading/cleaning and Brandon was cleaning.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5103,7 +5165,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,7 +5178,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Steven a and Brandon was cleaning</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5128,12 +5190,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5141,7 +5203,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
+          <t>Kemonica was cleaning and moving material</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5153,12 +5215,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5166,7 +5228,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
+          <t>The new guy was on the extruder too</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5178,7 +5240,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5191,7 +5253,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5203,7 +5265,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5216,7 +5278,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anthony was cleaning outside</t>
+          <t>Kemonica was grabbing material for various machines and cleaning</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5228,7 +5290,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5253,12 +5315,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5266,7 +5328,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Steven a was cleaning and Tevin was on the extruder with Brandon and Marcus</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5278,12 +5340,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5291,7 +5353,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Steven a was cleaning</t>
+          <t>Dee was transferring small boxes of bopp into big boxes as requested by Tim</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5303,12 +5365,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5316,7 +5378,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tony was cleaning around the auto tie</t>
+          <t>Brandon was on maintenance Steven a was cleaning Tevin was cleaning</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5328,12 +5390,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -5341,7 +5403,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Both Steven’s was cleaning and Steven a was also unloading a truck</t>
+          <t>Anthony was cleaning outside</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5353,12 +5415,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -5366,7 +5428,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Darius clean around autoroute for first 3 hours of shift</t>
+          <t>Steven a was cleaning</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5378,12 +5440,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5391,10 +5453,135 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
           <t>Steven a was cleaning</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Tony was cleaning around the auto tie</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Both Steven’s was cleaning and Steven a was also unloading a truck</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Darius clean around autoroute for first 3 hours of shift</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Steven a was cleaning</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
